--- a/exports/trend_1d/KOTAKBANK_full_report.xlsx
+++ b/exports/trend_1d/KOTAKBANK_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:U72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.64</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42037</v>
+        <v>42038</v>
       </c>
       <c r="H2" t="n">
-        <v>135.2</v>
+        <v>130.6</v>
       </c>
       <c r="I2" t="n">
         <v>130.706</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.43</v>
+        <v>-6.71</v>
       </c>
       <c r="L2" t="n">
-        <v>6.86</v>
+        <v>7.14</v>
       </c>
       <c r="M2" t="n">
         <v>0.93</v>
       </c>
       <c r="N2" t="n">
-        <v>2.67</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
         <v>0.65</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>10.56</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42062</v>
+        <v>42065</v>
       </c>
       <c r="H3" t="n">
-        <v>133.8</v>
+        <v>140.5</v>
       </c>
       <c r="I3" t="n">
         <v>137.0316971714573</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.45</v>
+        <v>-7.58</v>
       </c>
       <c r="L3" t="n">
-        <v>4.59</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>2.62</v>
+        <v>4.93</v>
       </c>
       <c r="N3" t="n">
-        <v>2.51</v>
+        <v>5.01</v>
       </c>
       <c r="O3" t="n">
         <v>-3.4</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>7.74</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H4" t="n">
-        <v>132.7</v>
+        <v>130.5</v>
       </c>
       <c r="I4" t="n">
         <v>131.4056486320716</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.55</v>
+        <v>-7.12</v>
       </c>
       <c r="L4" t="n">
-        <v>7.19</v>
+        <v>7.47</v>
       </c>
       <c r="M4" t="n">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="N4" t="n">
         <v>3.33</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>9.41</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42102</v>
+        <v>42103</v>
       </c>
       <c r="H5" t="n">
-        <v>137.2</v>
+        <v>143.1</v>
       </c>
       <c r="I5" t="n">
         <v>141.1878182234394</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.13</v>
+        <v>-9.66</v>
       </c>
       <c r="L5" t="n">
-        <v>8.279999999999999</v>
+        <v>10.65</v>
       </c>
       <c r="M5" t="n">
         <v>1.15</v>
       </c>
       <c r="N5" t="n">
-        <v>3.66</v>
+        <v>4.3</v>
       </c>
       <c r="O5" t="n">
         <v>-1.66</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>10.76</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42130</v>
+        <v>42131</v>
       </c>
       <c r="H6" t="n">
-        <v>135.1</v>
+        <v>130.8</v>
       </c>
       <c r="I6" t="n">
         <v>132.7532486527988</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-5.59</v>
+        <v>-8.6</v>
       </c>
       <c r="L6" t="n">
-        <v>9.359999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="M6" t="n">
         <v>2.03</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>13.32</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42179</v>
+        <v>42180</v>
       </c>
       <c r="H7" t="n">
-        <v>138.4</v>
+        <v>140.7</v>
       </c>
       <c r="I7" t="n">
         <v>139.341852923189</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.81</v>
+        <v>-7.57</v>
       </c>
       <c r="L7" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="M7" t="n">
         <v>0.6899999999999999</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>9.48</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42237</v>
+        <v>42240</v>
       </c>
       <c r="H8" t="n">
-        <v>137.6</v>
+        <v>129.5</v>
       </c>
       <c r="I8" t="n">
         <v>135.9527700682684</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.2</v>
+        <v>-7.96</v>
       </c>
       <c r="L8" t="n">
-        <v>4.62</v>
+        <v>10.38</v>
       </c>
       <c r="M8" t="n">
         <v>2.79</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>5.89</v>
       </c>
       <c r="O8" t="n">
         <v>1.66</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>11.44</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42306</v>
+        <v>42307</v>
       </c>
       <c r="H9" t="n">
-        <v>132.8</v>
+        <v>137.5</v>
       </c>
       <c r="I9" t="n">
         <v>135.9505126072753</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.55</v>
+        <v>-6.18</v>
       </c>
       <c r="L9" t="n">
-        <v>4.56</v>
+        <v>7.18</v>
       </c>
       <c r="M9" t="n">
         <v>1.62</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.65</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42383</v>
+        <v>42384</v>
       </c>
       <c r="H10" t="n">
-        <v>136.8</v>
+        <v>135.1</v>
       </c>
       <c r="I10" t="n">
         <v>136.1767389718891</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.51</v>
+        <v>-1.75</v>
       </c>
       <c r="L10" t="n">
         <v>7.71</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>7.65</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42452</v>
+        <v>42457</v>
       </c>
       <c r="H11" t="n">
-        <v>132</v>
+        <v>133.9</v>
       </c>
       <c r="I11" t="n">
         <v>133.3424347025805</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K11" t="n">
-        <v>2.29</v>
+        <v>0.89</v>
       </c>
       <c r="L11" t="n">
         <v>3.63</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>7.79</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H12" t="n">
-        <v>156.5</v>
+        <v>154.5</v>
       </c>
       <c r="I12" t="n">
         <v>155.9889190553538</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K12" t="n">
-        <v>16.88</v>
+        <v>15.38</v>
       </c>
       <c r="L12" t="n">
         <v>2.09</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>126</v>
+        <v>127</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.36</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42670</v>
+        <v>42671</v>
       </c>
       <c r="H13" t="n">
-        <v>161.3</v>
+        <v>163.9</v>
       </c>
       <c r="I13" t="n">
         <v>162.5238410014217</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.4</v>
+        <v>-6.08</v>
       </c>
       <c r="L13" t="n">
-        <v>6.28</v>
+        <v>6.41</v>
       </c>
       <c r="M13" t="n">
         <v>1.54</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.97</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42692</v>
+        <v>42695</v>
       </c>
       <c r="H14" t="n">
-        <v>155.8</v>
+        <v>152.5</v>
       </c>
       <c r="I14" t="n">
         <v>152.6834317955722</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.94</v>
+        <v>-6.96</v>
       </c>
       <c r="L14" t="n">
-        <v>7.02</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>4.06</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42758</v>
+        <v>42759</v>
       </c>
       <c r="H15" t="n">
-        <v>146.6</v>
+        <v>148.7</v>
       </c>
       <c r="I15" t="n">
         <v>146.9446449770685</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K15" t="n">
-        <v>3.87</v>
+        <v>2.49</v>
       </c>
       <c r="L15" t="n">
         <v>2.43</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.02</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42914</v>
+        <v>42915</v>
       </c>
       <c r="H16" t="n">
-        <v>194.4</v>
+        <v>189.7</v>
       </c>
       <c r="I16" t="n">
         <v>191.2709873190909</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K16" t="n">
-        <v>30.73</v>
+        <v>27.57</v>
       </c>
       <c r="L16" t="n">
         <v>1.28</v>
@@ -1353,7 +1544,7 @@
         <v>0.76</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O16" t="n">
         <v>1.43</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>6.77</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42943</v>
+        <v>42944</v>
       </c>
       <c r="H17" t="n">
-        <v>199.6</v>
+        <v>202.5</v>
       </c>
       <c r="I17" t="n">
         <v>200.267061728155</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.22</v>
+        <v>-6.75</v>
       </c>
       <c r="L17" t="n">
-        <v>7.17</v>
+        <v>7.27</v>
       </c>
       <c r="M17" t="n">
         <v>0.8</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>6.46</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43032</v>
+        <v>43033</v>
       </c>
       <c r="H18" t="n">
-        <v>213.1</v>
+        <v>202.1</v>
       </c>
       <c r="I18" t="n">
         <v>205.4682162162132</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K18" t="n">
-        <v>5.23</v>
+        <v>-0.2</v>
       </c>
       <c r="L18" t="n">
         <v>4.99</v>
@@ -1467,7 +1682,7 @@
         <v>1.46</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>5.16</v>
       </c>
       <c r="O18" t="n">
         <v>1.45</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.22</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43117</v>
+        <v>43118</v>
       </c>
       <c r="H19" t="n">
-        <v>205.4</v>
+        <v>209.3</v>
       </c>
       <c r="I19" t="n">
         <v>207.8945654509101</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.63</v>
+        <v>-3.56</v>
       </c>
       <c r="L19" t="n">
         <v>6.38</v>
@@ -1524,7 +1751,7 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="O19" t="n">
         <v>-5.16</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>4.9</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43136</v>
+        <v>43137</v>
       </c>
       <c r="H20" t="n">
-        <v>212.4</v>
+        <v>206.8</v>
       </c>
       <c r="I20" t="n">
         <v>209.6378380875782</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>1.48</v>
+        <v>-1.19</v>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>2.72</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="N20" t="n">
         <v>3.12</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>8.1</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43187</v>
+        <v>43192</v>
       </c>
       <c r="H21" t="n">
-        <v>209.6</v>
+        <v>219.3</v>
       </c>
       <c r="I21" t="n">
         <v>218.3330405189701</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.35</v>
+        <v>-6.04</v>
       </c>
       <c r="L21" t="n">
         <v>7.3</v>
@@ -1638,7 +1889,7 @@
         <v>0.91</v>
       </c>
       <c r="N21" t="n">
-        <v>2.22</v>
+        <v>4.63</v>
       </c>
       <c r="O21" t="n">
         <v>-2.64</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43300</v>
+        <v>43301</v>
       </c>
       <c r="H22" t="n">
-        <v>269.5</v>
+        <v>266.7</v>
       </c>
       <c r="I22" t="n">
         <v>267.9489450021236</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K22" t="n">
-        <v>22.89</v>
+        <v>21.61</v>
       </c>
       <c r="L22" t="n">
         <v>4.33</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.44</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43432</v>
+        <v>43433</v>
       </c>
       <c r="H23" t="n">
-        <v>232</v>
+        <v>242.6</v>
       </c>
       <c r="I23" t="n">
         <v>240.5779303509368</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K23" t="n">
-        <v>13.01</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="L23" t="n">
         <v>2.47</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.56</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43522</v>
+        <v>43523</v>
       </c>
       <c r="H24" t="n">
-        <v>247.2</v>
+        <v>243.2</v>
       </c>
       <c r="I24" t="n">
         <v>245.6866392400837</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9</v>
+        <v>0.25</v>
       </c>
       <c r="L24" t="n">
         <v>4.62</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>7.09</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43538</v>
+        <v>43539</v>
       </c>
       <c r="H25" t="n">
-        <v>253.8</v>
+        <v>265</v>
       </c>
       <c r="I25" t="n">
         <v>258.073669395123</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.36</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>5.06</v>
+        <v>10.16</v>
       </c>
       <c r="M25" t="n">
         <v>0.88</v>
       </c>
       <c r="N25" t="n">
-        <v>1.18</v>
+        <v>4.41</v>
       </c>
       <c r="O25" t="n">
         <v>-1.62</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>7.38</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43706</v>
+        <v>43707</v>
       </c>
       <c r="H26" t="n">
-        <v>290.2</v>
+        <v>286.3</v>
       </c>
       <c r="I26" t="n">
         <v>290.1850935918837</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K26" t="n">
-        <v>9.51</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>4.15</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>8.23</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H27" t="n">
-        <v>290.5</v>
+        <v>307.8</v>
       </c>
       <c r="I27" t="n">
         <v>304.4292756332005</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.47</v>
+        <v>-7.51</v>
       </c>
       <c r="L27" t="n">
-        <v>4.23</v>
+        <v>11.7</v>
       </c>
       <c r="M27" t="n">
         <v>0.39</v>
       </c>
       <c r="N27" t="n">
-        <v>2.23</v>
+        <v>5.96</v>
       </c>
       <c r="O27" t="n">
         <v>-1.34</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>9.59</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43847</v>
+        <v>43850</v>
       </c>
       <c r="H28" t="n">
-        <v>339.6</v>
+        <v>323.6</v>
       </c>
       <c r="I28" t="n">
         <v>329.3735722035807</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K28" t="n">
-        <v>10.33</v>
+        <v>5.13</v>
       </c>
       <c r="L28" t="n">
         <v>5.75</v>
@@ -2037,7 +2372,7 @@
         <v>0.99</v>
       </c>
       <c r="N28" t="n">
-        <v>3.28</v>
+        <v>4.71</v>
       </c>
       <c r="O28" t="n">
         <v>5.96</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>8.35</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43872</v>
+        <v>43873</v>
       </c>
       <c r="H29" t="n">
-        <v>335.5</v>
+        <v>343</v>
       </c>
       <c r="I29" t="n">
         <v>339.7544432272554</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.68</v>
+        <v>-6</v>
       </c>
       <c r="L29" t="n">
         <v>6.86</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>7.52</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43889</v>
+        <v>43892</v>
       </c>
       <c r="H30" t="n">
-        <v>324.1</v>
+        <v>319.8</v>
       </c>
       <c r="I30" t="n">
         <v>321.961542195568</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.51</v>
+        <v>-6.76</v>
       </c>
       <c r="L30" t="n">
-        <v>5.89</v>
+        <v>7.64</v>
       </c>
       <c r="M30" t="n">
         <v>1.66</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>7.61</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43983</v>
+        <v>43984</v>
       </c>
       <c r="H31" t="n">
-        <v>249.7</v>
+        <v>268.6</v>
       </c>
       <c r="I31" t="n">
         <v>264.0983365747608</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K31" t="n">
-        <v>21.92</v>
+        <v>16.01</v>
       </c>
       <c r="L31" t="n">
         <v>4.85</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>14.82</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44085</v>
+        <v>44088</v>
       </c>
       <c r="H32" t="n">
-        <v>266.1</v>
+        <v>260.9</v>
       </c>
       <c r="I32" t="n">
         <v>263.7570217534557</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.93</v>
+        <v>-2.87</v>
       </c>
       <c r="L32" t="n">
         <v>8.529999999999999</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>10.72</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44120</v>
+        <v>44123</v>
       </c>
       <c r="H33" t="n">
-        <v>267.3</v>
+        <v>275.3</v>
       </c>
       <c r="I33" t="n">
         <v>271.8015554910169</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.45</v>
+        <v>-5.52</v>
       </c>
       <c r="L33" t="n">
-        <v>4.71</v>
+        <v>5.79</v>
       </c>
       <c r="M33" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="O33" t="n">
         <v>-1.95</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.91</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44208</v>
+        <v>44209</v>
       </c>
       <c r="H34" t="n">
-        <v>380.7</v>
+        <v>376.4</v>
       </c>
       <c r="I34" t="n">
         <v>377.0233111079439</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K34" t="n">
-        <v>38.29</v>
+        <v>36.72</v>
       </c>
       <c r="L34" t="n">
         <v>3.12</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>6.59</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44230</v>
+        <v>44231</v>
       </c>
       <c r="H35" t="n">
-        <v>370.4</v>
+        <v>382.1</v>
       </c>
       <c r="I35" t="n">
         <v>375.2096263187275</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>1.59</v>
+        <v>-1.51</v>
       </c>
       <c r="L35" t="n">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="M35" t="n">
         <v>1.58</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>11.6</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44252</v>
+        <v>44253</v>
       </c>
       <c r="H36" t="n">
-        <v>379.1</v>
+        <v>356.1</v>
       </c>
       <c r="I36" t="n">
         <v>371.7788180439804</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.79</v>
+        <v>-6.8</v>
       </c>
       <c r="L36" t="n">
-        <v>4.16</v>
+        <v>7.2</v>
       </c>
       <c r="M36" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="N36" t="n">
-        <v>3.92</v>
+        <v>6.07</v>
       </c>
       <c r="O36" t="n">
         <v>3.16</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>13.49</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44412</v>
+        <v>44413</v>
       </c>
       <c r="H37" t="n">
-        <v>350</v>
+        <v>354.4</v>
       </c>
       <c r="I37" t="n">
         <v>351.9262699614354</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K37" t="n">
-        <v>1.71</v>
+        <v>0.48</v>
       </c>
       <c r="L37" t="n">
         <v>12.3</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>6</v>
+      </c>
+      <c r="U37" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.49</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H38" t="n">
-        <v>404.9</v>
+        <v>391.1</v>
       </c>
       <c r="I38" t="n">
         <v>404.4802849020774</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K38" t="n">
-        <v>14.25</v>
+        <v>10.36</v>
       </c>
       <c r="L38" t="n">
         <v>4.68</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.18</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H39" t="n">
-        <v>370.5</v>
+        <v>384.4</v>
       </c>
       <c r="I39" t="n">
         <v>378.3887322106621</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K39" t="n">
-        <v>5.27</v>
+        <v>1.71</v>
       </c>
       <c r="L39" t="n">
         <v>4.73</v>
@@ -2664,7 +3131,7 @@
         <v>1.7</v>
       </c>
       <c r="N39" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O39" t="n">
         <v>-3.41</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.529999999999999</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44599</v>
+        <v>44600</v>
       </c>
       <c r="H40" t="n">
-        <v>365.7</v>
+        <v>363.6</v>
       </c>
       <c r="I40" t="n">
         <v>364.6426094444052</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.86</v>
+        <v>-5.41</v>
       </c>
       <c r="L40" t="n">
         <v>7.28</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44701</v>
+        <v>44704</v>
       </c>
       <c r="H41" t="n">
-        <v>365.8</v>
+        <v>370.9</v>
       </c>
       <c r="I41" t="n">
         <v>370.3177034470567</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.61</v>
+        <v>-2.01</v>
       </c>
       <c r="L41" t="n">
         <v>5.23</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>7.15</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44721</v>
+        <v>44722</v>
       </c>
       <c r="H42" t="n">
-        <v>373</v>
+        <v>358.4</v>
       </c>
       <c r="I42" t="n">
         <v>359.2095725616452</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>0.57</v>
+        <v>-3.37</v>
       </c>
       <c r="L42" t="n">
-        <v>1.46</v>
+        <v>3.8</v>
       </c>
       <c r="M42" t="n">
-        <v>0.91</v>
+        <v>1.34</v>
       </c>
       <c r="N42" t="n">
-        <v>2.94</v>
+        <v>3.91</v>
       </c>
       <c r="O42" t="n">
         <v>1.39</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>9.33</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44755</v>
+        <v>44756</v>
       </c>
       <c r="H43" t="n">
-        <v>348.4</v>
+        <v>354</v>
       </c>
       <c r="I43" t="n">
         <v>353.3119925104047</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K43" t="n">
-        <v>2.79</v>
+        <v>1.23</v>
       </c>
       <c r="L43" t="n">
         <v>3.46</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>6.72</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44830</v>
+        <v>44831</v>
       </c>
       <c r="H44" t="n">
-        <v>365.8</v>
+        <v>359.9</v>
       </c>
       <c r="I44" t="n">
         <v>363.7160602728642</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K44" t="n">
-        <v>3.33</v>
+        <v>1.67</v>
       </c>
       <c r="L44" t="n">
         <v>2.12</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.390000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44876</v>
+        <v>44879</v>
       </c>
       <c r="H45" t="n">
-        <v>379.8</v>
+        <v>384.6</v>
       </c>
       <c r="I45" t="n">
         <v>383.1454652892141</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K45" t="n">
-        <v>-5.53</v>
+        <v>-6.86</v>
       </c>
       <c r="L45" t="n">
         <v>7.89</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>5.47</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44904</v>
+        <v>44907</v>
       </c>
       <c r="H46" t="n">
-        <v>377.6</v>
+        <v>373.2</v>
       </c>
       <c r="I46" t="n">
         <v>373.2273486858133</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.82</v>
+        <v>-2.96</v>
       </c>
       <c r="L46" t="n">
-        <v>2.39</v>
+        <v>3.12</v>
       </c>
       <c r="M46" t="n">
-        <v>0.93</v>
+        <v>1.22</v>
       </c>
       <c r="N46" t="n">
         <v>1.21</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.01</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45021</v>
+        <v>45022</v>
       </c>
       <c r="H47" t="n">
-        <v>350.4</v>
+        <v>351.4</v>
       </c>
       <c r="I47" t="n">
         <v>351.2591385636317</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K47" t="n">
-        <v>6.11</v>
+        <v>5.84</v>
       </c>
       <c r="L47" t="n">
         <v>0.86</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>4.85</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45084</v>
+        <v>45085</v>
       </c>
       <c r="H48" t="n">
-        <v>387.9</v>
+        <v>377.3</v>
       </c>
       <c r="I48" t="n">
         <v>378.4725508864348</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K48" t="n">
-        <v>10.39</v>
+        <v>7.37</v>
       </c>
       <c r="L48" t="n">
         <v>1</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>7.88</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45126</v>
+        <v>45127</v>
       </c>
       <c r="H49" t="n">
-        <v>381.3</v>
+        <v>391.4</v>
       </c>
       <c r="I49" t="n">
         <v>383.1658363746384</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.06</v>
+        <v>-3.74</v>
       </c>
       <c r="L49" t="n">
-        <v>2.68</v>
+        <v>4.03</v>
       </c>
       <c r="M49" t="n">
         <v>0.59</v>
       </c>
       <c r="N49" t="n">
-        <v>1.5</v>
+        <v>2.65</v>
       </c>
       <c r="O49" t="n">
         <v>-2.73</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,22 +3869,22 @@
         <v>6.37</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45135</v>
+        <v>45138</v>
       </c>
       <c r="H50" t="n">
-        <v>375.4</v>
+        <v>371.3</v>
       </c>
       <c r="I50" t="n">
         <v>374.4295535844053</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K50" t="n">
-        <v>-4.09</v>
+        <v>-5.14</v>
       </c>
       <c r="L50" t="n">
-        <v>5.14</v>
+        <v>5.52</v>
       </c>
       <c r="M50" t="n">
         <v>1.02</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>5.95</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45261</v>
+        <v>45264</v>
       </c>
       <c r="H51" t="n">
-        <v>350.1</v>
+        <v>363.7</v>
       </c>
       <c r="I51" t="n">
         <v>356.9352483265085</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="K51" t="n">
-        <v>5.71</v>
+        <v>2.05</v>
       </c>
       <c r="L51" t="n">
         <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>0.77</v>
+        <v>1.11</v>
       </c>
       <c r="N51" t="n">
-        <v>2.12</v>
+        <v>3.88</v>
       </c>
       <c r="O51" t="n">
         <v>-1.09</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>5</v>
+      </c>
+      <c r="U51" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>5.8</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45300</v>
+        <v>45301</v>
       </c>
       <c r="H52" t="n">
-        <v>365.3</v>
+        <v>364.2</v>
       </c>
       <c r="I52" t="n">
         <v>365.0468613534085</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K52" t="n">
-        <v>0.44</v>
+        <v>0.14</v>
       </c>
       <c r="L52" t="n">
         <v>3.63</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.83</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45378</v>
+        <v>45379</v>
       </c>
       <c r="H53" t="n">
-        <v>355.1</v>
+        <v>357.1</v>
       </c>
       <c r="I53" t="n">
         <v>356.3488340629288</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K53" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="L53" t="n">
         <v>2.2</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>4.8</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45406</v>
+        <v>45407</v>
       </c>
       <c r="H54" t="n">
-        <v>368.6</v>
+        <v>328.5</v>
       </c>
       <c r="I54" t="n">
         <v>346.2458338502058</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>3.22</v>
+        <v>-8.01</v>
       </c>
       <c r="L54" t="n">
-        <v>3.47</v>
+        <v>10.28</v>
       </c>
       <c r="M54" t="n">
-        <v>1.29</v>
+        <v>9.66</v>
       </c>
       <c r="N54" t="n">
-        <v>1.84</v>
+        <v>10.88</v>
       </c>
       <c r="O54" t="n">
         <v>0.5600000000000001</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.09</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45443</v>
+        <v>45446</v>
       </c>
       <c r="H55" t="n">
-        <v>336.1</v>
+        <v>343.6</v>
       </c>
       <c r="I55" t="n">
         <v>343.3567125628128</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.31</v>
+        <v>-4.6</v>
       </c>
       <c r="L55" t="n">
-        <v>4.84</v>
+        <v>5.88</v>
       </c>
       <c r="M55" t="n">
         <v>3.78</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.57</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45566</v>
+        <v>45568</v>
       </c>
       <c r="H56" t="n">
-        <v>375.9</v>
+        <v>364.6</v>
       </c>
       <c r="I56" t="n">
         <v>366.8068640954186</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="K56" t="n">
-        <v>9.4</v>
+        <v>6.11</v>
       </c>
       <c r="L56" t="n">
         <v>6.72</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>5</v>
+      </c>
+      <c r="U56" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.83</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45638</v>
+        <v>45639</v>
       </c>
       <c r="H57" t="n">
-        <v>353.7</v>
+        <v>361.1</v>
       </c>
       <c r="I57" t="n">
         <v>360.3376877651894</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K57" t="n">
-        <v>2.99</v>
+        <v>0.96</v>
       </c>
       <c r="L57" t="n">
         <v>5.1</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.69</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H58" t="n">
-        <v>426.4</v>
+        <v>407.6</v>
       </c>
       <c r="I58" t="n">
         <v>409.4033998135698</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K58" t="n">
-        <v>18.08</v>
+        <v>12.88</v>
       </c>
       <c r="L58" t="n">
         <v>4.51</v>
       </c>
       <c r="M58" t="n">
-        <v>1.31</v>
+        <v>5.32</v>
       </c>
       <c r="N58" t="n">
-        <v>3.21</v>
+        <v>4.41</v>
       </c>
       <c r="O58" t="n">
         <v>2.09</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>5</v>
+      </c>
+      <c r="U58" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.39</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45764</v>
+        <v>45768</v>
       </c>
       <c r="H59" t="n">
-        <v>437.6</v>
+        <v>448.3</v>
       </c>
       <c r="I59" t="n">
         <v>437.7379047942381</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.36</v>
+        <v>-9.99</v>
       </c>
       <c r="L59" t="n">
-        <v>7.65</v>
+        <v>10.94</v>
       </c>
       <c r="M59" t="n">
         <v>1.61</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>8.59</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45779</v>
+        <v>45782</v>
       </c>
       <c r="H60" t="n">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="I60" t="n">
         <v>420.6525577684787</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.52</v>
+        <v>-6.98</v>
       </c>
       <c r="L60" t="n">
-        <v>3.15</v>
+        <v>8.19</v>
       </c>
       <c r="M60" t="n">
-        <v>0.4</v>
+        <v>3.66</v>
       </c>
       <c r="N60" t="n">
-        <v>1.85</v>
+        <v>4.58</v>
       </c>
       <c r="O60" t="n">
         <v>2.45</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>9.1</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45817</v>
+        <v>45818</v>
       </c>
       <c r="H61" t="n">
-        <v>427.6</v>
+        <v>430.2</v>
       </c>
       <c r="I61" t="n">
         <v>429.048152330695</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.54</v>
+        <v>-3.17</v>
       </c>
       <c r="L61" t="n">
-        <v>3.76</v>
+        <v>4.22</v>
       </c>
       <c r="M61" t="n">
         <v>1.81</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>5.11</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H62" t="n">
-        <v>424.9</v>
+        <v>393.3</v>
       </c>
       <c r="I62" t="n">
         <v>420.7806357599846</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K62" t="n">
-        <v>-1.23</v>
+        <v>-8.58</v>
       </c>
       <c r="L62" t="n">
-        <v>3.67</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="M62" t="n">
-        <v>2.59</v>
+        <v>4.66</v>
       </c>
       <c r="N62" t="n">
-        <v>2.02</v>
+        <v>7.44</v>
       </c>
       <c r="O62" t="n">
         <v>0.61</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="H63" t="n">
-        <v>404.3</v>
+        <v>410.1</v>
       </c>
       <c r="I63" t="n">
         <v>407.8592189777447</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.8</v>
+        <v>-4.27</v>
       </c>
       <c r="L63" t="n">
         <v>4.53</v>
@@ -4041,7 +4796,19 @@
         <v>1</v>
       </c>
       <c r="Q63" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.15</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H64" t="n">
-        <v>427.4</v>
+        <v>420.4</v>
       </c>
       <c r="I64" t="n">
         <v>424.1527389375418</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K64" t="n">
-        <v>4.22</v>
+        <v>2.51</v>
       </c>
       <c r="L64" t="n">
         <v>3.9</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>6.71</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="H65" t="n">
-        <v>425.9</v>
+        <v>436</v>
       </c>
       <c r="I65" t="n">
         <v>433.9941819755603</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.31</v>
+        <v>-3.71</v>
       </c>
       <c r="L65" t="n">
-        <v>3.04</v>
+        <v>4.9</v>
       </c>
       <c r="M65" t="n">
         <v>0.75</v>
       </c>
       <c r="N65" t="n">
-        <v>1.64</v>
+        <v>2.37</v>
       </c>
       <c r="O65" t="n">
         <v>-1.64</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>5.86</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="H66" t="n">
-        <v>426.5</v>
+        <v>421</v>
       </c>
       <c r="I66" t="n">
         <v>422.9295662884845</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.18</v>
+        <v>-3.44</v>
       </c>
       <c r="L66" t="n">
-        <v>3.39</v>
+        <v>3.94</v>
       </c>
       <c r="M66" t="n">
         <v>0.44</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.44</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="H67" t="n">
-        <v>383.2</v>
+        <v>387.05</v>
       </c>
       <c r="I67" t="n">
         <v>385.5375598760752</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K67" t="n">
-        <v>8.98</v>
+        <v>8.06</v>
       </c>
       <c r="L67" t="n">
         <v>3.3</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>5</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>7.71</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="H68" t="n">
-        <v>396.75</v>
+        <v>381.3</v>
       </c>
       <c r="I68" t="n">
         <v>387.8006113345411</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K68" t="n">
-        <v>2.51</v>
+        <v>-1.49</v>
       </c>
       <c r="L68" t="n">
         <v>3.84</v>
       </c>
       <c r="M68" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="N68" t="n">
-        <v>3.3</v>
+        <v>3.89</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>8.02</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="H69" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I69" t="n">
         <v>399.9165185274731</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K69" t="n">
-        <v>-4.38</v>
+        <v>-4.9</v>
       </c>
       <c r="L69" t="n">
-        <v>4.45</v>
+        <v>4.9</v>
       </c>
       <c r="M69" t="n">
         <v>0.44</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>6.08</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H70" t="n">
-        <v>404</v>
+        <v>401.55</v>
       </c>
       <c r="I70" t="n">
         <v>402.4332700715389</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K70" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="L70" t="n">
         <v>3.38</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>5.02</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="H71" t="n">
-        <v>416</v>
+        <v>431.9</v>
       </c>
       <c r="I71" t="n">
         <v>421.7070445221612</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K71" t="n">
-        <v>-3.6</v>
+        <v>-7.56</v>
       </c>
       <c r="L71" t="n">
         <v>8.48</v>
@@ -4488,7 +5339,7 @@
         <v>2.16</v>
       </c>
       <c r="N71" t="n">
-        <v>2.71</v>
+        <v>3.82</v>
       </c>
       <c r="O71" t="n">
         <v>-0.61</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4548,6 +5411,14 @@
       <c r="Q72" t="n">
         <v>16</v>
       </c>
+      <c r="R72" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9506,7 +10377,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.4</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="6">
@@ -9516,7 +10387,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7">
@@ -9526,7 +10397,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8">
@@ -9536,7 +10407,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9546,7 +10417,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87.2</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="10">
@@ -9556,7 +10427,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -9596,7 +10467,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.36</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="15">
@@ -9606,7 +10477,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.53</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="16">
@@ -9616,7 +10487,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.19</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="17">
@@ -9626,7 +10497,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>38.29</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="18">
@@ -9636,7 +10507,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.1</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="19">
@@ -9646,7 +10517,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.72</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="20">
@@ -9656,7 +10527,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.54</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="21">
@@ -9676,7 +10547,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
@@ -9686,7 +10557,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -9696,7 +10567,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -9706,7 +10577,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.01</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="26">
@@ -9716,7 +10587,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="27">
@@ -9736,7 +10607,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
